--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128520246</v>
+        <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93215</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mjösjön, Mpd</t>
+          <t>Dysjön harrån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526504</v>
+        <v>526593</v>
       </c>
       <c r="R3" t="n">
-        <v>6939676</v>
+        <v>6939747</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,38 +888,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128520246</t>
+          <t>https://artportalen.se/Sighting/136866620</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128520248</v>
+        <v>128520246</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>93215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526624</v>
+        <v>526504</v>
       </c>
       <c r="R4" t="n">
-        <v>6939869</v>
+        <v>6939676</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,6 +989,220 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128520246</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136866619</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93437</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dysjön harrån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>526587</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6939759</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866619</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128520248</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mjösjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>526624</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6939869</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128520248</t>
         </is>
@@ -989,6 +1213,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18081-2025 artfynd.xlsx
+++ b/artfynd/A 18081-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136866620</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136866619</v>
       </c>
       <c r="B5" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
